--- a/public/exports/facebook-ambulances-marketplace-bulk.xlsx
+++ b/public/exports/facebook-ambulances-marketplace-bulk.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="COMPLIANCE NOTES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WHY PREVIOUS FILE FAILED" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Bulk Upload Template" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VALIDATION" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
@@ -465,114 +465,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="120" customWidth="1" style="8" min="1" max="1"/>
+    <col width="110" customWidth="1" style="8" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Facebook Marketplace compliance notes for this upload</t>
+          <t>Facebook template review / fix notes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>This file fills Meta's official Bulk Upload Template for 5 non-running diesel ambulances.</t>
+          <t>Errors found in the previous upload file:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Do not edit the Bulk Upload Template header rows (1-4).</t>
+          <t>1) CONDITION must be exactly one of VALIDATION values, including the special en-dash character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Wrong: Used - Fair</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>How this file is written to fit Marketplace / Commerce policies:</t>
+          <t xml:space="preserve">   Correct: 'Used – fair'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. Accurate condition: Used - Fair; clearly states DOES NOT RUN / not roadworthy.</t>
+          <t>2) CATEGORY is required by the spreadsheet dropdown (allowBlank=False), even though the header says OPTIONAL.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2. Real price $1500 (not bait pricing).</t>
+          <t xml:space="preserve">   Wrong: blank</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Salvage title and VIN/mileage disclosed.</t>
+          <t xml:space="preserve">   Correct: Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4. No medical devices, drugs, or patient-care supplies are offered (those are restricted on Marketplace).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5. Distinct listings (different VINs) — not duplicate spam.</t>
+          <t xml:space="preserve">   (This goods bulk template has no Vehicles category. Non-running project/parts ambulances fit Car Parts &amp; Accessories.)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6. Seller identified (Prince George Transport); local pickup only in Blythewood, SC.</t>
+          <t>UPLOAD THIS FILE: facebook-ambulances-marketplace-bulk-UPLOAD.xlsx (Bulk Upload Template + VALIDATION only).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7. Category left blank: this bulk goods template has no Vehicles category. For a dedicated Vehicles listing with year/make/model fields, post manually under Marketplace → Vehicles instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>8. Photos are not part of this XLSX — add your own original photos from facebook-ambulances-listing-pack.zip when creating/finishing listings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>9. Upload only once; do not repost the same VIN repeatedly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10. You are responsible for complying with Meta Commerce Policies, Community Standards, and SC title/sale laws.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Upload: Marketplace bulk upload / seller tools that accept this template. Keep COMPLIANCE NOTES sheet or delete it before upload if the tool rejects extra sheets.</t>
+          <t>Do not upload the notes workbook if your tool rejects extra sheets.</t>
         </is>
       </c>
     </row>
@@ -590,11 +562,11 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" style="8" min="1" max="1"/>
+    <col width="40" customWidth="1" style="8" min="2" max="2"/>
+    <col width="40" customWidth="1" style="8" min="3" max="3"/>
+    <col width="40" customWidth="1" style="8" min="4" max="4"/>
+    <col width="40" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,7 +656,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>2008 Ford E-350 Diesel Ambulance Not Running Project/Parts $1500</t>
+          <t>2008 Ford E-350 Diesel Ambulance Not Running Project/Parts</t>
         </is>
       </c>
       <c r="B5" s="0" t="n">
@@ -692,174 +664,198 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Used - Fair</t>
+          <t>Used – fair</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>FOR SALE: 2008 Ford E-350 Super Duty diesel Type II ambulance — Truck 1.
+          <t>FOR SALE: 2008 Ford E-350 Super Duty diesel Type II ambulance - Truck 1.
 IMPORTANT: This vehicle DOES NOT RUN. Sold as a non-running project, parts donor, or ambulance body only. Not roadworthy. Sold as-is, where-is, with no warranty.
 VIN: 1FDSS34P88DA70177
 License: 5525PN
 Odometer: 365,027 miles
 Title status: Salvage (confirm at pickup)
 Details:
-• 6.0L V8 diesel
-• New transmission installed at 347,847 miles (2023)
-• Headlights replaced; new tires and brakes
-• Outdoor-stored retired fleet unit
-• No medical equipment, drugs, or patient-care supplies included
-Price: $1,500 (firm unless otherwise agreed)
+- 6.0L V8 diesel
+- New transmission installed at 347,847 miles (2023)
+- Headlights replaced; new tires and brakes
+- Outdoor-stored retired fleet unit
+- No medical equipment, drugs, or patient-care supplies included
+Price: $1,500
 Local pickup only: 200 Louthian Way, Blythewood, SC 29016
 Buyer arranges and pays for all towing/transport.
 Seller: Prince George Transport (licensed SC non-emergency ambulance service).
 Call/text: (803) 231-9420
-Please confirm VIN, title, and mileage in person before paying.
-Serious local buyers only. No shipping of the vehicle by seller.</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="n"/>
+Confirm VIN, title, and mileage in person before paying.
+Serious local buyers only.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2008 Ford E-350 Diesel Ambulance Not Running Project/Parts $1500</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>2008 Ford E-350 Diesel Ambulance Not Running Project/Parts</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
         <v>1500</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Used - Fair</t>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Used – fair</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>FOR SALE: 2008 Ford E-350 Super Duty diesel Type II ambulance — Truck 2.
+          <t>FOR SALE: 2008 Ford E-350 Super Duty diesel Type II ambulance - Truck 2.
 IMPORTANT: This vehicle DOES NOT RUN. Sold as a non-running project, parts donor, or ambulance body only. Not roadworthy. Sold as-is, where-is, with no warranty.
 VIN: 1FDSS34P58DB04415
 License: SS25PN
 Odometer: 176,487 miles
 Title status: Salvage (confirm at pickup)
 Details:
-• Diesel
-• Injectors replaced in 2023
-• Outdoor-stored retired fleet unit
-• No medical equipment, drugs, or patient-care supplies included
-Price: $1,500 (firm unless otherwise agreed)
+- Diesel
+- Injectors replaced in 2023
+- Outdoor-stored retired fleet unit
+- No medical equipment, drugs, or patient-care supplies included
+Price: $1,500
 Local pickup only: 200 Louthian Way, Blythewood, SC 29016
 Buyer arranges and pays for all towing/transport.
 Seller: Prince George Transport (licensed SC non-emergency ambulance service).
 Call/text: (803) 231-9420
-Please confirm VIN, title, and mileage in person before paying.
-Serious local buyers only. No shipping of the vehicle by seller.</t>
+Confirm VIN, title, and mileage in person before paying.
+Serious local buyers only.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2010 Ford E-350 Diesel Ambulance Not Running Project/Parts $1500</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2010 Ford E-350 Diesel Ambulance Not Running Project/Parts</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
         <v>1500</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Used - Fair</t>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Used – fair</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>FOR SALE: 2010 Ford E-350 Super Duty diesel Type II ambulance — Truck 3.
+          <t>FOR SALE: 2010 Ford E-350 Super Duty diesel Type II ambulance - Truck 3.
 IMPORTANT: This vehicle DOES NOT RUN. Sold as a non-running project, parts donor, or ambulance body only. Not roadworthy. Sold as-is, where-is, with no warranty.
 VIN: 1FDSS3EPADA25619
 Odometer: 355,825 miles
 Title status: Salvage (confirm at pickup)
 Details:
-• Diesel
-• Outdoor-stored retired fleet unit
-• No medical equipment, drugs, or patient-care supplies included
-Price: $1,500 (firm unless otherwise agreed)
+- Diesel
+- Outdoor-stored retired fleet unit
+- No medical equipment, drugs, or patient-care supplies included
+Price: $1,500
 Local pickup only: 200 Louthian Way, Blythewood, SC 29016
 Buyer arranges and pays for all towing/transport.
 Seller: Prince George Transport (licensed SC non-emergency ambulance service).
 Call/text: (803) 231-9420
-Please confirm VIN, title, and mileage in person before paying.
-Serious local buyers only. No shipping of the vehicle by seller.</t>
+Confirm VIN, title, and mileage in person before paying.
+Serious local buyers only.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2009 Ford E-350 Diesel Ambulance Not Running Project/Parts $1500</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>2009 Ford E-350 Diesel Ambulance Not Running Project/Parts</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
         <v>1500</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Used - Fair</t>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Used – fair</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>FOR SALE: 2009 Ford E-350 Super Duty diesel Type II ambulance — Truck 4.
+          <t>FOR SALE: 2009 Ford E-350 Super Duty diesel Type II ambulance - Truck 4.
 IMPORTANT: This vehicle DOES NOT RUN. Sold as a non-running project, parts donor, or ambulance body only. Not roadworthy. Sold as-is, where-is, with no warranty.
 VIN: 1FDSSES2ADA88103
 Odometer: 346,618 miles
 Title status: Salvage (confirm at pickup)
 Details:
-• Diesel
-• Refurbished AC — condition unknown
-• Outdoor-stored retired fleet unit
-• No medical equipment, drugs, or patient-care supplies included
-Price: $1,500 (firm unless otherwise agreed)
+- Diesel
+- Refurbished AC - condition unknown
+- Outdoor-stored retired fleet unit
+- No medical equipment, drugs, or patient-care supplies included
+Price: $1,500
 Local pickup only: 200 Louthian Way, Blythewood, SC 29016
 Buyer arranges and pays for all towing/transport.
 Seller: Prince George Transport (licensed SC non-emergency ambulance service).
 Call/text: (803) 231-9420
-Please confirm VIN, title, and mileage in person before paying.
-Serious local buyers only. No shipping of the vehicle by seller.</t>
+Confirm VIN, title, and mileage in person before paying.
+Serious local buyers only.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2010 Ford E-350 Diesel Ambulance Not Running Project/Parts $1500</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>2010 Ford E-350 Diesel Ambulance Not Running Project/Parts</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
         <v>1500</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Used - Fair</t>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Used – fair</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>FOR SALE: 2010 Ford E-350 Super Duty diesel Type II ambulance — Truck 5.
+          <t>FOR SALE: 2010 Ford E-350 Super Duty diesel Type II ambulance - Truck 5.
 IMPORTANT: This vehicle DOES NOT RUN. Sold as a non-running project, parts donor, or ambulance body only. Not roadworthy. Sold as-is, where-is, with no warranty.
 VIN: 1FDSSEP7ADA03185
 Odometer: 377,409 miles
 Title status: Salvage (confirm at pickup)
 Details:
-• Diesel
-• Outdoor-stored retired fleet unit
-• No medical equipment, drugs, or patient-care supplies included
-Price: $1,500 (firm unless otherwise agreed)
+- Diesel
+- Outdoor-stored retired fleet unit
+- No medical equipment, drugs, or patient-care supplies included
+Price: $1,500
 Local pickup only: 200 Louthian Way, Blythewood, SC 29016
 Buyer arranges and pays for all towing/transport.
 Seller: Prince George Transport (licensed SC non-emergency ambulance service).
 Call/text: (803) 231-9420
-Please confirm VIN, title, and mileage in person before paying.
-Serious local buyers only. No shipping of the vehicle by seller.</t>
+Confirm VIN, title, and mileage in person before paying.
+Serious local buyers only.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Auto Parts &amp; Accessories//Car Parts &amp; Accessories</t>
         </is>
       </c>
     </row>
